--- a/data/trans_camb/P16A_n_R3-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A_n_R3-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 1,61</t>
+          <t>-1,98; 1,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 2,02</t>
+          <t>-1,63; 1,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 2,62</t>
+          <t>-0,59; 2,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 3,27</t>
+          <t>-1,84; 3,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 1,68</t>
+          <t>-2,29; 1,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,95</t>
+          <t>0,46; 4,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,54</t>
+          <t>-1,31; 1,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 1,07</t>
+          <t>-1,46; 1,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,27</t>
+          <t>0,59; 3,36</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 237,83</t>
+          <t>-100,0; 254,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-79,24; 298,23</t>
+          <t>-72,94; 260,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-33,61; 345,24</t>
+          <t>-31,09; 363,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-67,44; 522,88</t>
+          <t>-68,57; 396,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-86,9; 294,7</t>
+          <t>-80,72; 323,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 674,81</t>
+          <t>2,05; 669,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-61,47; 163,59</t>
+          <t>-59,97; 157,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-60,36; 111,58</t>
+          <t>-61,8; 118,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,86; 320,3</t>
+          <t>19,52; 366,32</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 3,6</t>
+          <t>-0,17; 3,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,7</t>
+          <t>-1,5; 0,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,94</t>
+          <t>1,98; 6,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,97</t>
+          <t>0,36; 3,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 2,8</t>
+          <t>0,0; 3,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,09; 6,7</t>
+          <t>3,18; 6,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,97</t>
+          <t>0,37; 2,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,36</t>
+          <t>-0,47; 1,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 5,75</t>
+          <t>2,94; 5,76</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-68,84; —</t>
+          <t>-50,67; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83,79; 2283,65</t>
+          <t>71,3; 2311,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-32,1; —</t>
+          <t>-15,68; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>182,03; —</t>
+          <t>195,23; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,2; 1174,57</t>
+          <t>7,67; 1037,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-58,57; 509,77</t>
+          <t>-60,9; 611,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>247,49; 2143,8</t>
+          <t>236,58; 2095,81</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 3,64</t>
+          <t>-0,12; 3,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,02</t>
+          <t>-1,65; 0,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 5,88</t>
+          <t>-0,58; 5,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 3,8</t>
+          <t>-2,5; 3,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 8,87</t>
+          <t>-1,26; 7,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,35; 14,24</t>
+          <t>5,37; 14,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 3,23</t>
+          <t>-0,23; 2,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,99</t>
+          <t>-1,16; 1,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 7,27</t>
+          <t>0,29; 7,23</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-22,5; 459,41</t>
+          <t>-22,18; 422,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-79,32; 161,87</t>
+          <t>-80,17; 147,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,72; 585,87</t>
+          <t>-19,16; 550,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-64,48; 336,23</t>
+          <t>-65,23; 340,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-41,4; 739,91</t>
+          <t>-40,96; 683,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>87,01; 1069,91</t>
+          <t>69,37; 1087,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 291,6</t>
+          <t>-14,9; 284,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-48,6; 164,86</t>
+          <t>-52,04; 163,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,59; 523,9</t>
+          <t>17,25; 508,78</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,97</t>
+          <t>-1,07; 1,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 1,13</t>
+          <t>-0,87; 1,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,51; 5,52</t>
+          <t>2,74; 5,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 2,91</t>
+          <t>-0,65; 2,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 2,61</t>
+          <t>-0,85; 2,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 4,4</t>
+          <t>-0,26; 4,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,5</t>
+          <t>-0,48; 1,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,23</t>
+          <t>-0,52; 1,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,49</t>
+          <t>1,57; 4,42</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-50,25; 74,98</t>
+          <t>-48,55; 75,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-41,97; 84,89</t>
+          <t>-37,89; 102,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>101,32; 421,41</t>
+          <t>111,62; 436,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-19,2; 189,98</t>
+          <t>-21,52; 201,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-27,81; 177,72</t>
+          <t>-26,66; 175,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 248,03</t>
+          <t>-2,33; 265,93</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,55; 91,59</t>
+          <t>-20,4; 84,5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-20,65; 78,5</t>
+          <t>-22,78; 80,54</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>75,97; 286,09</t>
+          <t>69,36; 288,0</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 1,34</t>
+          <t>-2,69; 1,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 2,77</t>
+          <t>-1,17; 2,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,73</t>
+          <t>1,0; 5,65</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,87; 6,16</t>
+          <t>2,03; 6,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,97</t>
+          <t>1,87; 6,04</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,88; 14,76</t>
+          <t>8,33; 15,25</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,77</t>
+          <t>0,79; 3,78</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,99</t>
+          <t>1,04; 3,9</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,48; 10,85</t>
+          <t>6,57; 10,95</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-70,28; 121,77</t>
+          <t>-73,3; 102,25</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-38,13; 259,41</t>
+          <t>-39,67; 205,19</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22,53; 481,21</t>
+          <t>19,99; 453,45</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>52,86; 534,06</t>
+          <t>61,27; 501,59</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>48,4; 490,86</t>
+          <t>57,25; 504,91</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>244,48; 1278,25</t>
+          <t>273,32; 1256,37</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,22; 268,61</t>
+          <t>23,84; 230,24</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>26,97; 249,93</t>
+          <t>32,0; 255,4</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>227,18; 753,15</t>
+          <t>205,62; 692,78</t>
         </is>
       </c>
     </row>
@@ -1762,42 +1762,42 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,49</t>
+          <t>0,58; 3,37</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,45; 5,3</t>
+          <t>1,57; 5,37</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,23; 4,1</t>
+          <t>0,44; 4,31</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,92; 11,15</t>
+          <t>6,86; 11,18</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,34</t>
+          <t>1,18; 4,42</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,34</t>
+          <t>0,35; 3,35</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5,35; 8,96</t>
+          <t>5,27; 8,84</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>30,76; 176,71</t>
+          <t>35,28; 178,17</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3,58; 136,34</t>
+          <t>9,24; 142,66</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>149,87; 380,96</t>
+          <t>145,79; 376,55</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>29,18; 173,97</t>
+          <t>29,92; 177,12</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>7,97; 140,31</t>
+          <t>7,6; 135,94</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>143,69; 376,03</t>
+          <t>137,25; 378,85</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 1,04</t>
+          <t>-0,37; 0,97</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,76</t>
+          <t>-0,45; 0,75</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,94</t>
+          <t>1,97; 3,92</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,34</t>
+          <t>1,41; 3,4</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,68</t>
+          <t>0,9; 2,63</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,82; 7,65</t>
+          <t>4,82; 7,66</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,96</t>
+          <t>0,82; 1,97</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,55</t>
+          <t>0,42; 1,56</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,91; 5,65</t>
+          <t>3,82; 5,55</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-18,45; 84,99</t>
+          <t>-21,69; 78,99</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-23,07; 65,31</t>
+          <t>-25,57; 62,74</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>113,14; 328,12</t>
+          <t>111,37; 317,29</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>52,33; 149,67</t>
+          <t>48,9; 154,98</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>29,18; 122,37</t>
+          <t>26,79; 117,14</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>164,17; 341,36</t>
+          <t>175,32; 365,07</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>36,27; 108,2</t>
+          <t>34,69; 107,41</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>20,84; 86,11</t>
+          <t>17,17; 87,42</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>177,55; 317,94</t>
+          <t>177,3; 313,72</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A_n_R3-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A_n_R3-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,1</t>
+          <t>1,18</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,86</t>
+          <t>2,97</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,94</t>
+          <t>2,04</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 1,49</t>
+          <t>-2,13; 1,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 1,76</t>
+          <t>-1,59; 2,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 2,72</t>
+          <t>-0,71; 2,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 3,03</t>
+          <t>-1,44; 3,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 1,62</t>
+          <t>-2,53; 1,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,86</t>
+          <t>0,47; 5,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,5</t>
+          <t>-1,33; 1,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,13</t>
+          <t>-1,38; 1,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,36</t>
+          <t>0,62; 3,37</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>159,58%</t>
+          <t>165,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>118,18%</t>
+          <t>123,96%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 254,54</t>
+          <t>-100,0; 198,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-72,94; 260,76</t>
+          <t>-71,51; 277,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-31,09; 363,53</t>
+          <t>-34,02; 375,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-68,57; 396,15</t>
+          <t>-63,56; 439,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-80,72; 323,59</t>
+          <t>-83,11; 231,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,05; 669,72</t>
+          <t>1,78; 711,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-59,97; 157,87</t>
+          <t>-61,32; 163,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-61,8; 118,22</t>
+          <t>-60,67; 134,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,52; 366,32</t>
+          <t>15,99; 349,87</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,82</t>
+          <t>3,64</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,9</t>
+          <t>4,79</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4,33</t>
+          <t>4,19</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 3,56</t>
+          <t>-0,2; 3,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,63</t>
+          <t>-1,46; 0,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 6,13</t>
+          <t>2,05; 5,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,93</t>
+          <t>0,14; 3,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,1</t>
+          <t>-0,18; 2,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,18; 6,8</t>
+          <t>3,01; 6,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,94</t>
+          <t>0,45; 2,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,28</t>
+          <t>-0,53; 1,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,76</t>
+          <t>2,91; 5,56</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>525,69%</t>
+          <t>501,24%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>945,08%</t>
+          <t>923,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>695,41%</t>
+          <t>672,99%</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-50,67; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71,3; 2311,98</t>
+          <t>78,97; 1969,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,68; —</t>
+          <t>-58,35; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>195,23; —</t>
+          <t>171,5; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,67; 1037,1</t>
+          <t>20,99; 1253,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-60,9; 611,37</t>
+          <t>-60,41; 440,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>236,58; 2095,81</t>
+          <t>230,27; 2354,22</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>4,97</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,71</t>
+          <t>9,37</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,07</t>
+          <t>6,29</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 3,56</t>
+          <t>-0,13; 3,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,98</t>
+          <t>-1,68; 1,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 5,97</t>
+          <t>2,87; 7,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 3,97</t>
+          <t>-2,84; 3,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 7,59</t>
+          <t>-1,74; 8,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,37; 14,51</t>
+          <t>4,91; 13,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 2,98</t>
+          <t>-0,36; 2,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,87</t>
+          <t>-1,04; 1,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 7,23</t>
+          <t>4,29; 8,65</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>186,46%</t>
+          <t>339,96%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>334,68%</t>
+          <t>323,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>225,82%</t>
+          <t>349,23%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-22,18; 422,13</t>
+          <t>-22,69; 499,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-80,17; 147,07</t>
+          <t>-79,22; 146,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 550,14</t>
+          <t>110,87; 904,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-65,23; 340,86</t>
+          <t>-66,04; 327,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-40,96; 683,88</t>
+          <t>-48,66; 558,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>69,37; 1087,86</t>
+          <t>79,67; 1215,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-14,9; 284,03</t>
+          <t>-20,87; 239,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-52,04; 163,07</t>
+          <t>-44,37; 182,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,25; 508,78</t>
+          <t>146,77; 747,31</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,01</t>
+          <t>3,87</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,5</t>
+          <t>3,72</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,33</t>
+          <t>3,84</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 1,02</t>
+          <t>-1,25; 0,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,26</t>
+          <t>-1,1; 1,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,74; 5,52</t>
+          <t>2,49; 5,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,92</t>
+          <t>-0,42; 2,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 2,65</t>
+          <t>-0,81; 2,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 4,44</t>
+          <t>2,03; 5,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 1,37</t>
+          <t>-0,54; 1,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 1,29</t>
+          <t>-0,51; 1,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,42</t>
+          <t>2,66; 4,92</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>223,2%</t>
+          <t>215,61%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>108,0%</t>
+          <t>161,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>168,08%</t>
+          <t>193,65%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-48,55; 75,27</t>
+          <t>-53,65; 76,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-37,89; 102,18</t>
+          <t>-46,91; 91,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>111,62; 436,9</t>
+          <t>89,98; 402,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-21,52; 201,38</t>
+          <t>-17,93; 173,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-26,66; 175,93</t>
+          <t>-28,1; 153,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 265,93</t>
+          <t>58,48; 354,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-20,4; 84,5</t>
+          <t>-23,3; 85,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-22,78; 80,54</t>
+          <t>-22,24; 91,77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>69,36; 288,0</t>
+          <t>104,15; 326,11</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,36</t>
+          <t>2,69</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,96</t>
+          <t>12,85</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8,85</t>
+          <t>8,73</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 1,17</t>
+          <t>-2,59; 1,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 2,81</t>
+          <t>-1,27; 2,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,65</t>
+          <t>0,4; 4,9</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,03; 6,23</t>
+          <t>2,09; 6,19</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,87; 6,04</t>
+          <t>1,6; 5,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,33; 15,25</t>
+          <t>10,64; 14,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,78</t>
+          <t>0,68; 3,65</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,9</t>
+          <t>0,94; 3,94</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,57; 10,95</t>
+          <t>7,02; 10,42</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>143,05%</t>
+          <t>114,39%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>581,84%</t>
+          <t>625,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>408,27%</t>
+          <t>402,79%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-73,3; 102,25</t>
+          <t>-71,68; 147,78</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-39,67; 205,19</t>
+          <t>-37,71; 236,84</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19,99; 453,45</t>
+          <t>6,03; 376,62</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>61,27; 501,59</t>
+          <t>60,41; 510,6</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>57,25; 504,91</t>
+          <t>46,59; 483,57</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>273,32; 1256,37</t>
+          <t>326,33; 1294,91</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,84; 230,24</t>
+          <t>22,17; 233,82</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>32,0; 255,4</t>
+          <t>29,15; 260,51</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>205,62; 692,78</t>
+          <t>227,26; 715,77</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,51</t>
+          <t>1,53</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,05</t>
+          <t>8,89</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7,07</t>
+          <t>7,18</t>
         </is>
       </c>
     </row>
@@ -1762,42 +1762,42 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>0,0; 2,31</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,37</t>
+          <t>0,62; 3,45</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,37</t>
+          <t>1,57; 5,31</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,31</t>
+          <t>0,61; 4,07</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,86; 11,18</t>
+          <t>6,9; 10,95</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,42</t>
+          <t>1,29; 4,43</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,35</t>
+          <t>0,31; 3,35</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5,27; 8,84</t>
+          <t>5,47; 8,92</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>243,33%</t>
+          <t>238,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>235,32%</t>
+          <t>238,96%</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>35,28; 178,17</t>
+          <t>30,04; 171,01</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>9,24; 142,66</t>
+          <t>11,15; 137,95</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>145,79; 376,55</t>
+          <t>146,29; 366,79</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>29,92; 177,12</t>
+          <t>33,29; 184,44</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>7,6; 135,94</t>
+          <t>7,37; 138,94</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>137,25; 378,85</t>
+          <t>142,85; 374,3</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3,04</t>
+          <t>3,25</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,5</t>
+          <t>7,08</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4,83</t>
+          <t>5,22</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,97</t>
+          <t>-0,27; 1,06</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,75</t>
+          <t>-0,46; 0,77</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,97; 3,92</t>
+          <t>2,48; 4,03</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,4</t>
+          <t>1,51; 3,33</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,63</t>
+          <t>0,97; 2,8</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,82; 7,66</t>
+          <t>6,23; 8,06</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,97</t>
+          <t>0,84; 1,95</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,56</t>
+          <t>0,43; 1,52</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,82; 5,55</t>
+          <t>4,65; 5,82</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>205,65%</t>
+          <t>219,55%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>252,66%</t>
+          <t>275,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>237,27%</t>
+          <t>256,59%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-21,69; 78,99</t>
+          <t>-16,59; 82,3</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-25,57; 62,74</t>
+          <t>-25,91; 62,86</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>111,37; 317,29</t>
+          <t>132,57; 334,6</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>48,9; 154,98</t>
+          <t>53,36; 152,54</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>26,79; 117,14</t>
+          <t>33,04; 129,62</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>175,32; 365,07</t>
+          <t>206,47; 367,21</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>34,69; 107,41</t>
+          <t>36,96; 106,62</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>17,17; 87,42</t>
+          <t>19,0; 84,63</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>177,3; 313,72</t>
+          <t>199,67; 328,39</t>
         </is>
       </c>
     </row>
